--- a/Analysis/Phase2TableSummaryServices.xlsx
+++ b/Analysis/Phase2TableSummaryServices.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gx1/Git/Unina/LLM/VulnEnvLLM/Analysis/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gx1/Git/Unina/LLM/LLM-Generation-Intentionally-Vulnerable-Dockerfiles/Analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D9C0613-E463-FB40-9C6D-74CA9BD6BF73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58F92E29-57DD-5E47-83C5-D9B316257C34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17780" xr2:uid="{ED262890-8FBF-8042-A14A-DB41F6FE7956}"/>
+    <workbookView xWindow="38400" yWindow="-1440" windowWidth="21600" windowHeight="37900" xr2:uid="{ED262890-8FBF-8042-A14A-DB41F6FE7956}"/>
   </bookViews>
   <sheets>
     <sheet name="Services" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="19">
   <si>
     <t>CVE-ID</t>
   </si>
@@ -72,9 +72,6 @@
   </si>
   <si>
     <t>CVE-2017-16082</t>
-  </si>
-  <si>
-    <t>CVE-2017-17405</t>
   </si>
   <si>
     <t>CVE-2018-3760</t>
@@ -467,7 +464,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6823FC06-1C58-D34C-A89C-EFE8575596A7}">
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.42578125" customWidth="1"/>
@@ -481,13 +478,13 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D1" t="s">
         <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -711,7 +708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>11</v>
       </c>
@@ -739,7 +736,7 @@
         <v>1</v>
       </c>
       <c r="D16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -756,7 +753,7 @@
         <v>1</v>
       </c>
       <c r="D17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -770,7 +767,7 @@
         <v>4</v>
       </c>
       <c r="C18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -787,7 +784,7 @@
         <v>5</v>
       </c>
       <c r="C19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -821,10 +818,10 @@
         <v>5</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -838,7 +835,7 @@
         <v>4</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -855,10 +852,10 @@
         <v>5</v>
       </c>
       <c r="C23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -875,7 +872,7 @@
         <v>1</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -889,46 +886,12 @@
         <v>5</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>17</v>
-      </c>
-      <c r="B26" t="s">
-        <v>4</v>
-      </c>
-      <c r="C26">
-        <v>1</v>
-      </c>
-      <c r="D26">
-        <v>1</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>17</v>
-      </c>
-      <c r="B27" t="s">
-        <v>5</v>
-      </c>
-      <c r="C27">
-        <v>1</v>
-      </c>
-      <c r="D27">
-        <v>1</v>
-      </c>
-      <c r="E27">
         <v>0</v>
       </c>
     </row>

--- a/Analysis/Phase2TableSummaryServices.xlsx
+++ b/Analysis/Phase2TableSummaryServices.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gx1/Git/Unina/LLM/LLM-Generation-Intentionally-Vulnerable-Dockerfiles/Analysis/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gx1/Git/Unina/LLM-Generation-Intentionally-Vulnerable-Dockerfiles/Analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58F92E29-57DD-5E47-83C5-D9B316257C34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A092BAE-25C2-8142-A6D1-D217DE4360E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38400" yWindow="-1440" windowWidth="21600" windowHeight="37900" xr2:uid="{ED262890-8FBF-8042-A14A-DB41F6FE7956}"/>
+    <workbookView xWindow="38400" yWindow="500" windowWidth="21600" windowHeight="21100" xr2:uid="{ED262890-8FBF-8042-A14A-DB41F6FE7956}"/>
   </bookViews>
   <sheets>
     <sheet name="Services" sheetId="1" r:id="rId1"/>
@@ -535,7 +535,7 @@
         <v>1</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
